--- a/DataTables/Datas/condition.xlsx
+++ b/DataTables/Datas/condition.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\Hippo-s-Epic\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{115B76E3-1911-4A2F-AE80-F3C5459852C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6A5410A-A48A-4B13-A2BF-27ECE0BBD087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="50">
   <si>
     <t>##var</t>
   </si>
@@ -177,6 +177,18 @@
   </si>
   <si>
     <t>拳王被河马打爆</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>开局对话条件</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>配空默认完成</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>教练拳击馆对话条件</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -203,16 +215,23 @@
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -227,13 +246,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -536,7 +557,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="17.125" customWidth="1"/>
@@ -649,177 +670,216 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>30</v>
+    <row r="5" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B5" s="4">
+        <v>0</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
         <v>28</v>
       </c>
+      <c r="E6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" t="s">
+        <v>29</v>
+      </c>
       <c r="G6" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="I6" s="2" t="s">
-        <v>42</v>
-      </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>31</v>
       </c>
+      <c r="D7" t="s">
+        <v>28</v>
+      </c>
       <c r="G7" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>31</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="H9">
-        <v>1002001</v>
+        <v>31</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B10">
-        <v>6</v>
-      </c>
-      <c r="C10" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" t="s">
-        <v>28</v>
+        <v>5</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H10">
+        <v>1002001</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C11" t="s">
         <v>35</v>
       </c>
       <c r="D11" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C12" t="s">
-        <v>34</v>
-      </c>
-      <c r="H12">
-        <v>1002001</v>
+        <v>35</v>
+      </c>
+      <c r="D12" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>37</v>
-      </c>
-      <c r="D13" t="s">
-        <v>38</v>
+        <v>34</v>
+      </c>
+      <c r="H13">
+        <v>1002001</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C14" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D14" t="s">
-        <v>28</v>
-      </c>
-      <c r="H14">
-        <v>1002001</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B15">
-        <v>11</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>40</v>
+        <v>10</v>
+      </c>
+      <c r="C15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" t="s">
+        <v>28</v>
+      </c>
+      <c r="H15">
+        <v>1002001</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B16">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="H16">
-        <v>1003004</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B17">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>34</v>
       </c>
       <c r="H17">
+        <v>1003004</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B18">
+        <v>13</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H18">
         <v>1003005</v>
       </c>
-      <c r="I17" s="2" t="s">
+      <c r="I18" s="2" t="s">
         <v>44</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" s="4" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B19" s="4">
+        <v>14</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H19" s="4">
+        <v>1005001</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" s="4" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B20" s="4">
+        <v>15</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H20" s="4">
+        <v>1006001</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/DataTables/Datas/condition.xlsx
+++ b/DataTables/Datas/condition.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\Hippo-s-Epic\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6A5410A-A48A-4B13-A2BF-27ECE0BBD087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AAEAB07-7786-4883-B06E-CD61CC010F17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="57">
   <si>
     <t>##var</t>
   </si>
@@ -189,6 +189,34 @@
   </si>
   <si>
     <t>教练拳击馆对话条件</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>找到牙了</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>教练被打瘪了</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>拳王被打败了</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>你打九龙疯了</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>拳王打九龙疯了</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>地图下水道解锁</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>地图内城解锁</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -246,7 +274,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -255,6 +283,8 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -557,7 +587,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="17.125" customWidth="1"/>
@@ -882,6 +912,83 @@
         <v>49</v>
       </c>
     </row>
+    <row r="21" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B21" s="6">
+        <v>16</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B22" s="6">
+        <v>17</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="I22" s="7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B23" s="6">
+        <v>18</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="I23" s="7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B24" s="6">
+        <v>19</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="I24" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B25" s="6">
+        <v>20</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="I25" s="7" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9" s="4" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B26" s="4">
+        <v>21</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9" s="4" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B27" s="4">
+        <v>22</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/DataTables/Datas/condition.xlsx
+++ b/DataTables/Datas/condition.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\Hippo-s-Epic\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AAEAB07-7786-4883-B06E-CD61CC010F17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65C16672-20FB-4D99-BFB8-BF64395BEDC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="61">
   <si>
     <t>##var</t>
   </si>
@@ -217,6 +217,22 @@
   </si>
   <si>
     <t>地图内城解锁</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>把道具假牙（1004）交给教练</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>持有假牙</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>持有报道</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>100-1</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -587,7 +603,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="17.125" customWidth="1"/>
@@ -856,7 +872,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B17">
         <v>12</v>
       </c>
@@ -870,7 +886,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B18">
         <v>13</v>
       </c>
@@ -884,7 +900,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="2:9" s="4" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:10" s="4" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B19" s="4">
         <v>14</v>
       </c>
@@ -898,7 +914,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="20" spans="2:9" s="4" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:10" s="4" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B20" s="4">
         <v>15</v>
       </c>
@@ -912,7 +928,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="21" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:10" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B21" s="6">
         <v>16</v>
       </c>
@@ -922,8 +938,11 @@
       <c r="I21" s="7" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="22" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="J21" s="7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B22" s="6">
         <v>17</v>
       </c>
@@ -934,7 +953,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="23" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:10" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B23" s="6">
         <v>18</v>
       </c>
@@ -945,7 +964,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="24" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:10" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B24" s="6">
         <v>19</v>
       </c>
@@ -956,7 +975,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="25" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:10" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B25" s="6">
         <v>20</v>
       </c>
@@ -967,26 +986,54 @@
         <v>54</v>
       </c>
     </row>
-    <row r="26" spans="2:9" s="4" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:10" s="4" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B26" s="4">
         <v>21</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>34</v>
       </c>
+      <c r="D26" s="5" t="s">
+        <v>60</v>
+      </c>
       <c r="I26" s="5" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="27" spans="2:9" s="4" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:10" s="4" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B27" s="4">
         <v>22</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>34</v>
       </c>
+      <c r="D27" s="5" t="s">
+        <v>60</v>
+      </c>
       <c r="I27" s="5" t="s">
         <v>56</v>
+      </c>
+    </row>
+    <row r="28" spans="2:10" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B28" s="4">
+        <v>23</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="I28" s="7" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="29" spans="2:10" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B29" s="4">
+        <v>24</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="I29" s="7" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/DataTables/Datas/condition.xlsx
+++ b/DataTables/Datas/condition.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\Hippo-s-Epic\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65C16672-20FB-4D99-BFB8-BF64395BEDC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{363944EE-3E9B-4A08-9FA7-F0BB3E78911C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="62">
   <si>
     <t>##var</t>
   </si>
@@ -69,170 +69,224 @@
     <t>##</t>
   </si>
   <si>
-    <t>0无条件判断仅占位
+    <t>物品id,数量</t>
+  </si>
+  <si>
+    <t>任务id,进度</t>
+  </si>
+  <si>
+    <t>战斗ID,胜负(1胜利2失败)</t>
+  </si>
+  <si>
+    <t>竖杠隔开的是后面物品、任务状态、特质三个字段对应的判断</t>
+  </si>
+  <si>
+    <t>##comment</t>
+  </si>
+  <si>
+    <t>条件唯一标识</t>
+  </si>
+  <si>
+    <t>判断</t>
+  </si>
+  <si>
+    <t>是否有某物品</t>
+  </si>
+  <si>
+    <t>某任务状态</t>
+  </si>
+  <si>
+    <t>是否有某个特质</t>
+  </si>
+  <si>
+    <t>战斗id与结果条件</t>
+  </si>
+  <si>
+    <t>需要完成对话的id</t>
+  </si>
+  <si>
+    <t>2-3|4|4|4|0</t>
+  </si>
+  <si>
+    <t>1-1</t>
+  </si>
+  <si>
+    <t>1|2</t>
+  </si>
+  <si>
+    <t>2002-1</t>
+  </si>
+  <si>
+    <t>0|0|0|5|0</t>
+  </si>
+  <si>
+    <t>2003-2</t>
+  </si>
+  <si>
+    <t>2004-2</t>
+  </si>
+  <si>
+    <t>0|0|0|0|5</t>
+  </si>
+  <si>
+    <t>2|0|0|0|0</t>
+  </si>
+  <si>
+    <t>2-1</t>
+  </si>
+  <si>
+    <t>1-2|0|0|0|0</t>
+  </si>
+  <si>
+    <t>1-3</t>
+  </si>
+  <si>
+    <t>2|0|0|0|5</t>
+  </si>
+  <si>
+    <t>2-1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1-2|0|0|0|0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>教练和拳王的战斗</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>给教练报纸的分支</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>河马上台打的分支</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>河马被拳王打爆</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>拳王被河马打爆</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>开局对话条件</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>配空默认完成</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>教练拳击馆对话条件</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>教练被打瘪了</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>拳王被打败了</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>你打九龙疯了</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>拳王打九龙疯了</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>地图下水道解锁</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>地图内城解锁</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>把道具假牙（1004）交给教练</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>持有假牙</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>持有报道</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>100-1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1004-1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1002-1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">条件需要按照顺序去配置
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">为物品|任务|特质|战斗|对话id
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">0无条件判断仅占位
 1大于条件数量
 2等于条件数量
 3小于数量条件
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>前三个仅对物品数量判断有效，4和5仅对后面的判断有效</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
 4满足部分条件
 5满住全部条件</t>
-  </si>
-  <si>
-    <t>物品id,数量</t>
-  </si>
-  <si>
-    <t>任务id,进度</t>
-  </si>
-  <si>
-    <t>战斗ID,胜负(1胜利2失败)</t>
-  </si>
-  <si>
-    <t>竖杠隔开的是后面物品、任务状态、特质三个字段对应的判断</t>
-  </si>
-  <si>
-    <t>##comment</t>
-  </si>
-  <si>
-    <t>条件唯一标识</t>
-  </si>
-  <si>
-    <t>判断</t>
-  </si>
-  <si>
-    <t>是否有某物品</t>
-  </si>
-  <si>
-    <t>某任务状态</t>
-  </si>
-  <si>
-    <t>是否有某个特质</t>
-  </si>
-  <si>
-    <t>战斗id与结果条件</t>
-  </si>
-  <si>
-    <t>需要完成对话的id</t>
-  </si>
-  <si>
-    <t>2-3|4|4|4|0</t>
-  </si>
-  <si>
-    <t>1-1</t>
-  </si>
-  <si>
-    <t>1|2</t>
-  </si>
-  <si>
-    <t>2002-1</t>
-  </si>
-  <si>
-    <t>0|0|0|5|0</t>
-  </si>
-  <si>
-    <t>2003-2</t>
-  </si>
-  <si>
-    <t>2004-2</t>
-  </si>
-  <si>
-    <t>0|0|0|0|5</t>
-  </si>
-  <si>
-    <t>2|0|0|0|0</t>
-  </si>
-  <si>
-    <t>2-1</t>
-  </si>
-  <si>
-    <t>1-2|0|0|0|0</t>
-  </si>
-  <si>
-    <t>1-3</t>
-  </si>
-  <si>
-    <t>2|0|0|0|5</t>
-  </si>
-  <si>
-    <t>2-1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1-2|0|0|0|0</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>教练和拳王的战斗</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>给教练报纸的分支</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>河马上台打的分支</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>河马被拳王打爆</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>拳王被河马打爆</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>开局对话条件</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>配空默认完成</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>教练拳击馆对话条件</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>找到牙了</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>教练被打瘪了</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>拳王被打败了</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>你打九龙疯了</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>拳王打九龙疯了</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>地图下水道解锁</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>地图内城解锁</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>把道具假牙（1004）交给教练</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>持有假牙</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>持有报道</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>100-1</t>
+    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -240,7 +294,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -258,6 +312,14 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -603,12 +665,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="17.125" customWidth="1"/>
     <col min="2" max="2" width="18.75" customWidth="1"/>
-    <col min="3" max="3" width="18.125" customWidth="1"/>
+    <col min="3" max="3" width="33.5" customWidth="1"/>
     <col min="4" max="4" width="20.5" customWidth="1"/>
     <col min="5" max="5" width="15.75" customWidth="1"/>
     <col min="6" max="8" width="16.625" customWidth="1"/>
@@ -670,50 +732,50 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="81" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:9" ht="142.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>13</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D3" t="s">
         <v>14</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>15</v>
       </c>
-      <c r="E3" t="s">
+      <c r="G3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" t="s">
         <v>19</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>20</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>21</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>22</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>23</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.15">
@@ -721,10 +783,10 @@
         <v>0</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.15">
@@ -732,19 +794,19 @@
         <v>1</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" t="s">
         <v>27</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" t="s">
         <v>28</v>
       </c>
-      <c r="E6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="G6" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.15">
@@ -752,16 +814,16 @@
         <v>2</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.15">
@@ -769,13 +831,13 @@
         <v>3</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="G8" s="2" t="s">
-        <v>32</v>
-      </c>
       <c r="I8" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.15">
@@ -783,13 +845,13 @@
         <v>4</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.15">
@@ -797,7 +859,7 @@
         <v>5</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H10">
         <v>1002001</v>
@@ -808,10 +870,10 @@
         <v>6</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.15">
@@ -819,10 +881,10 @@
         <v>7</v>
       </c>
       <c r="C12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" t="s">
         <v>35</v>
-      </c>
-      <c r="D12" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.15">
@@ -830,7 +892,7 @@
         <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H13">
         <v>1002001</v>
@@ -841,10 +903,10 @@
         <v>9</v>
       </c>
       <c r="C14" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" t="s">
         <v>37</v>
-      </c>
-      <c r="D14" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.15">
@@ -852,10 +914,10 @@
         <v>10</v>
       </c>
       <c r="C15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H15">
         <v>1002001</v>
@@ -866,174 +928,180 @@
         <v>11</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.15">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B17">
         <v>12</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H17">
         <v>1003004</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.15">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B18">
         <v>13</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H18">
         <v>1003005</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="19" spans="2:10" s="4" customFormat="1" x14ac:dyDescent="0.15">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" s="4" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B19" s="4">
         <v>14</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H19" s="4">
         <v>1005001</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="20" spans="2:10" s="4" customFormat="1" x14ac:dyDescent="0.15">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" s="4" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B20" s="4">
         <v>15</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H20" s="4">
         <v>1006001</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="21" spans="2:10" s="6" customFormat="1" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B21" s="6">
         <v>16</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
+      </c>
+      <c r="H21" s="6">
+        <v>1007003</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="J21" s="7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="22" spans="2:10" s="6" customFormat="1" x14ac:dyDescent="0.15">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B22" s="6">
         <v>17</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="23" spans="2:10" s="6" customFormat="1" x14ac:dyDescent="0.15">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B23" s="6">
         <v>18</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="24" spans="2:10" s="6" customFormat="1" x14ac:dyDescent="0.15">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B24" s="6">
         <v>19</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="25" spans="2:10" s="6" customFormat="1" x14ac:dyDescent="0.15">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B25" s="6">
         <v>20</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="26" spans="2:10" s="4" customFormat="1" x14ac:dyDescent="0.15">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9" s="4" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B26" s="4">
         <v>21</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="27" spans="2:10" s="4" customFormat="1" x14ac:dyDescent="0.15">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9" s="4" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B27" s="4">
         <v>22</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="28" spans="2:10" s="6" customFormat="1" x14ac:dyDescent="0.15">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B28" s="4">
         <v>23</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>59</v>
       </c>
       <c r="I28" s="7" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="29" spans="2:10" s="6" customFormat="1" x14ac:dyDescent="0.15">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="29" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B29" s="4">
         <v>24</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>60</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
